--- a/storage/workspaces/facturas/output/resaltado_facturas.xlsx
+++ b/storage/workspaces/facturas/output/resaltado_facturas.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI451"/>
+  <dimension ref="A1:AI461"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43372,6 +43372,956 @@
         <v>21536106453</v>
       </c>
       <c r="AI451" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Maribel Perez Ibáñez &lt;tormofelipe@angulo.es&gt;</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>24/06/2025</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>8243-13528658.xlsx</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>8243-13528658</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>30/05/2025</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>24695195461</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Urbanización Esteban Alberto 97 Puerta 4  Segovia, 68385</t>
+        </is>
+      </c>
+      <c r="L452" t="n">
+        <v>25888624403</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Urbanización Rocío Lledó 89 Cáceres, 27241</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>jex-44113</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Magni vel autem similique recusandae assumenda atque quam corporis sed.</t>
+        </is>
+      </c>
+      <c r="R452" t="n">
+        <v>542153.16</v>
+      </c>
+      <c r="Y452" t="n">
+        <v>32200775574340</v>
+      </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="AB452" t="n">
+        <v>542153.16</v>
+      </c>
+      <c r="AD452" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF452" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH452" t="n">
+        <v>25888624403</v>
+      </c>
+      <c r="AI452" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Cruz Perales-Bayón &lt;adelia22@moles.es&gt;</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>22/06/2025</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>4040-96186554.xlsx</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>4040-96186554</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>25558175597</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>C. de Valentín Amaya 1 Puerta 2  Ciudad, 86808</t>
+        </is>
+      </c>
+      <c r="L453" t="n">
+        <v>28979346307</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Paseo Morena Palacio 946 Apt. 53  Ávila, 25102</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>lQG-34431</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Quae consequuntur vel soluta suscipit veniam iste cupiditate animi recusandae aperiam modi.</t>
+        </is>
+      </c>
+      <c r="R453" t="n">
+        <v>458122.26</v>
+      </c>
+      <c r="Y453" t="n">
+        <v>54796183870355</v>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>15/01/2025</t>
+        </is>
+      </c>
+      <c r="AB453" t="n">
+        <v>458122.26</v>
+      </c>
+      <c r="AD453" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF453" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH453" t="n">
+        <v>28979346307</v>
+      </c>
+      <c r="AI453" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Rogelio del Blanca &lt;riosjuanito@hotmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>29/06/2025</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>5023-42361690.xlsx</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>5023-42361690</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>09/06/2025</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>26154240534</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Rambla de José Manuel Cuéllar 68 Salamanca, 62917</t>
+        </is>
+      </c>
+      <c r="L454" t="n">
+        <v>22526205273</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Via Custodio Gimenez 4 Piso 6  Teruel, 63045</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>dVM-81869</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Tempora earum error cupiditate ex saepe consectetur ab numquam odio.</t>
+        </is>
+      </c>
+      <c r="R454" t="n">
+        <v>165834.78</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>81873635133592</v>
+      </c>
+      <c r="Z454" t="inlineStr">
+        <is>
+          <t>11/06/2025</t>
+        </is>
+      </c>
+      <c r="AB454" t="n">
+        <v>165834.78</v>
+      </c>
+      <c r="AD454" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF454" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH454" t="n">
+        <v>22526205273</v>
+      </c>
+      <c r="AI454" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Emiliano Marc Vilar Roldan &lt;hmanso@hotmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>14/07/2025</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>6390-01407842.xlsx</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>6390-01407842</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>17/11/2023</t>
+        </is>
+      </c>
+      <c r="H455" t="n">
+        <v>20998628965</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Pasadizo Salvador Sabater 70 Pontevedra, 29086</t>
+        </is>
+      </c>
+      <c r="L455" t="n">
+        <v>29274265918</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Paseo de Jonatan Ayuso 778 Apt. 72  Valladolid, 41313</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>mRF-21695</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Amet voluptatibus deleniti reiciendis sint quibusdam non quod suscipit modi natus veritatis quibusdam.</t>
+        </is>
+      </c>
+      <c r="R455" t="n">
+        <v>453277.42</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>87514660146922</v>
+      </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t>19/11/2023</t>
+        </is>
+      </c>
+      <c r="AB455" t="n">
+        <v>453277.42</v>
+      </c>
+      <c r="AD455" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF455" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH455" t="n">
+        <v>29274265918</v>
+      </c>
+      <c r="AI455" t="inlineStr">
+        <is>
+          <t>Autorizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Visitación Bou Carbó &lt;ztellez@saldana-guardia.net&gt;</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>12/07/2025</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>9594-74695053.xlsx</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>9594-74695053</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="H456" t="n">
+        <v>26224926428</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Pasaje de Nilda Bustamante 61 Madrid, 80747</t>
+        </is>
+      </c>
+      <c r="L456" t="n">
+        <v>30697410236</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Pasadizo Julie Rozas 9 Santa Cruz de Tenerife, 04474</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Lav-50188</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Sunt quasi libero nihil at quia ad odit quas quia.</t>
+        </is>
+      </c>
+      <c r="R456" t="n">
+        <v>370479.11</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>17010902820873</v>
+      </c>
+      <c r="Z456" t="inlineStr">
+        <is>
+          <t>16/03/2025</t>
+        </is>
+      </c>
+      <c r="AB456" t="n">
+        <v>370479.11</v>
+      </c>
+      <c r="AD456" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF456" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH456" t="n">
+        <v>30697410236</v>
+      </c>
+      <c r="AI456" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Cebrián Valbuena Bayón &lt;gutierreznereida@yahoo.com&gt;</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>8098-31898428.xlsx</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>8098-31898428</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>29/01/2025</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>30700976669</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Rambla Cesar González 3 Puerta 1  Madrid, 08825</t>
+        </is>
+      </c>
+      <c r="L457" t="n">
+        <v>28221113366</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Pasadizo de Remedios Chico 55 Apt. 83  Tarragona, 08957</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>fXG-39318</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Commodi laborum quisquam tempore natus placeat architecto totam veritatis aspernatur.</t>
+        </is>
+      </c>
+      <c r="R457" t="n">
+        <v>443557.15</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>70620068733142</v>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>05/02/2025</t>
+        </is>
+      </c>
+      <c r="AB457" t="n">
+        <v>443557.15</v>
+      </c>
+      <c r="AD457" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF457" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AH457" t="n">
+        <v>28221113366</v>
+      </c>
+      <c r="AI457" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>María Luisa Aguilar Roca &lt;estercarballo@pazos.net&gt;</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>12/07/2025</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>6085-32020399.xlsx</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>6085-32020399</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>28/03/2024</t>
+        </is>
+      </c>
+      <c r="H458" t="n">
+        <v>27711760429</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Urbanización de Serafina Pou 598 Cantabria, 34357</t>
+        </is>
+      </c>
+      <c r="L458" t="n">
+        <v>20439754700</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Cañada Gonzalo Herranz 7 Piso 8  Jaén, 03010</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>JOy-73246</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Optio dolorum vitae libero id autem voluptatum minima iusto quia ex officia qui.</t>
+        </is>
+      </c>
+      <c r="R458" t="n">
+        <v>187686.76</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>30810795018270</v>
+      </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t>29/03/2024</t>
+        </is>
+      </c>
+      <c r="AB458" t="n">
+        <v>187686.76</v>
+      </c>
+      <c r="AD458" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF458" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH458" t="n">
+        <v>20439754700</v>
+      </c>
+      <c r="AI458" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Blas Saez Toro &lt;zuriarte@coca-duenas.com&gt;</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>06/07/2025</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>0054-70813845.xlsx</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>0054-70813845</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>21/08/2024</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>30943852507</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Acceso de Flavio Sosa 5 Piso 2  Cantabria, 99812</t>
+        </is>
+      </c>
+      <c r="L459" t="n">
+        <v>29800804458</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Camino de Juliana Calvo 846 Apt. 04  Lugo, 26552</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>xex-78512</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>Nesciunt quia alias eveniet expedita sed blanditiis perspiciatis fugiat.</t>
+        </is>
+      </c>
+      <c r="R459" t="n">
+        <v>95310.67999999999</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>33197736026072</v>
+      </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t>26/08/2024</t>
+        </is>
+      </c>
+      <c r="AB459" t="n">
+        <v>95310.67999999999</v>
+      </c>
+      <c r="AD459" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF459" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH459" t="n">
+        <v>29800804458</v>
+      </c>
+      <c r="AI459" t="inlineStr">
+        <is>
+          <t>Fecha no coincide</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Milagros Tenorio &lt;bcornejo@becerra-lerma.es&gt;</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>27/06/2025</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>3493-09724653.xlsx</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>3493-09724653</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>20/08/2023</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>30540474257</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Plaza Danilo Ribas 706 Burgos, 04442</t>
+        </is>
+      </c>
+      <c r="L460" t="n">
+        <v>23675193453</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Rambla de Rolando Izquierdo 23 Córdoba, 64273</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>qod-04777</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Odio consectetur deleniti a vitae voluptates accusantium ut neque totam ut.</t>
+        </is>
+      </c>
+      <c r="R460" t="n">
+        <v>241119.82</v>
+      </c>
+      <c r="Y460" t="n">
+        <v>24689506209336</v>
+      </c>
+      <c r="Z460" t="inlineStr">
+        <is>
+          <t>25/08/2023</t>
+        </is>
+      </c>
+      <c r="AB460" t="n">
+        <v>241119.82</v>
+      </c>
+      <c r="AD460" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AF460" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AH460" t="n">
+        <v>23675193453</v>
+      </c>
+      <c r="AI460" t="inlineStr">
+        <is>
+          <t>CAE no encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Nereida Sanjuan-Mata &lt;torrijosnazario@lumbreras.com&gt;</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>05/07/2025</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>7469-88253383.xlsx</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>7469-88253383</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>24/09/2024</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>25378761984</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Vial de Victoria Arrieta 87 Puerta 4  Valencia, 73304</t>
+        </is>
+      </c>
+      <c r="L461" t="n">
+        <v>27702353678</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>I.V.A. RESPONSABLE INSCRIPTO</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Callejón Valero Pombo 8 Apt. 48  Alicante, 10214</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>NVh-60112</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Non doloribus error doloremque minima libero nihil exercitationem sint omnis ipsa.</t>
+        </is>
+      </c>
+      <c r="R461" t="n">
+        <v>830570.05</v>
+      </c>
+      <c r="Y461" t="n">
+        <v>16846739564402</v>
+      </c>
+      <c r="Z461" t="inlineStr">
+        <is>
+          <t>06/10/2024</t>
+        </is>
+      </c>
+      <c r="AB461" t="n">
+        <v>830570.05</v>
+      </c>
+      <c r="AD461" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF461" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AH461" t="n">
+        <v>27702353678</v>
+      </c>
+      <c r="AI461" t="inlineStr">
         <is>
           <t>Autorizado</t>
         </is>
